--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128466224</v>
+        <v>128466277</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462469</v>
+        <v>462757</v>
       </c>
       <c r="R2" t="n">
-        <v>6697194</v>
+        <v>6696682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128466251</v>
+        <v>128466270</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,34 +811,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462497</v>
+        <v>462777</v>
       </c>
       <c r="R3" t="n">
-        <v>6697135</v>
+        <v>6696623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +900,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,32 +919,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128466222</v>
+        <v>128466271</v>
       </c>
       <c r="B4" t="n">
-        <v>91480</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462417</v>
+        <v>462729</v>
       </c>
       <c r="R4" t="n">
-        <v>6697315</v>
+        <v>6696784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128466245</v>
+        <v>128466272</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462529</v>
+        <v>462727</v>
       </c>
       <c r="R5" t="n">
-        <v>6697126</v>
+        <v>6696783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128466265</v>
+        <v>128466273</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,37 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462675</v>
+        <v>462356</v>
       </c>
       <c r="R6" t="n">
-        <v>6696895</v>
+        <v>6697346</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,12 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1222,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128466260</v>
+        <v>128466274</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462377</v>
+        <v>462446</v>
       </c>
       <c r="R7" t="n">
-        <v>6697267</v>
+        <v>6697105</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,12 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128466266</v>
+        <v>128466275</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1362,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462594</v>
+        <v>462670</v>
       </c>
       <c r="R8" t="n">
-        <v>6696982</v>
+        <v>6696759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,12 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På 3-4 tallstammar.</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,43 +1462,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128466221</v>
+        <v>128466276</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462534</v>
+        <v>462797</v>
       </c>
       <c r="R9" t="n">
-        <v>6697251</v>
+        <v>6696603</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst ca. Flertal i större "mycelring".</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128466231</v>
+        <v>128466241</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,34 +1593,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462657</v>
+        <v>462466</v>
       </c>
       <c r="R10" t="n">
-        <v>6696882</v>
+        <v>6697178</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1673,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,6 +1682,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1688,48 +1701,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128466274</v>
+        <v>128466242</v>
       </c>
       <c r="B11" t="n">
-        <v>92806</v>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462446</v>
+        <v>462476</v>
       </c>
       <c r="R11" t="n">
-        <v>6697105</v>
+        <v>6697152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128466230</v>
+        <v>128466233</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,35 +1820,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1846,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462362</v>
+        <v>462380</v>
       </c>
       <c r="R12" t="n">
-        <v>6697282</v>
+        <v>6697276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,6 +1901,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1918,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128466253</v>
+        <v>128466235</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,34 +1931,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462421</v>
+        <v>462540</v>
       </c>
       <c r="R13" t="n">
-        <v>6697341</v>
+        <v>6696867</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,6 +2012,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2025,45 +2031,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128466248</v>
+        <v>128466236</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462651</v>
+        <v>462733</v>
       </c>
       <c r="R14" t="n">
-        <v>6696877</v>
+        <v>6696654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2105,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,6 +2123,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2132,44 +2142,36 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128466270</v>
+        <v>128466238</v>
       </c>
       <c r="B15" t="n">
-        <v>92806</v>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2213,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,32 +2253,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128466249</v>
+        <v>128466222</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2286,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462756</v>
+        <v>462417</v>
       </c>
       <c r="R16" t="n">
-        <v>6696647</v>
+        <v>6697315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,45 +2360,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128466244</v>
+        <v>128466258</v>
       </c>
       <c r="B17" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462583</v>
+        <v>462346</v>
       </c>
       <c r="R17" t="n">
-        <v>6696944</v>
+        <v>6697328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2438,7 +2443,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,6 +2457,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2465,45 +2476,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128466243</v>
+        <v>128466260</v>
       </c>
       <c r="B18" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462628</v>
+        <v>462377</v>
       </c>
       <c r="R18" t="n">
-        <v>6696967</v>
+        <v>6697267</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2535,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2545,7 +2559,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,6 +2573,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2572,45 +2592,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128466271</v>
+        <v>128466261</v>
       </c>
       <c r="B19" t="n">
-        <v>92806</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462729</v>
+        <v>462748</v>
       </c>
       <c r="R19" t="n">
-        <v>6696784</v>
+        <v>6696705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2642,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2652,7 +2675,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,6 +2689,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2679,42 +2708,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128466227</v>
+        <v>128466262</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2722,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462484</v>
+        <v>462731</v>
       </c>
       <c r="R20" t="n">
-        <v>6697200</v>
+        <v>6696782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2767,12 +2791,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På äldre grövre tallstam.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,6 +2805,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2799,46 +2824,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128466232</v>
+        <v>128466263</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2846,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462418</v>
+        <v>462702</v>
       </c>
       <c r="R21" t="n">
-        <v>6697314</v>
+        <v>6696765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2881,7 +2897,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2891,7 +2907,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Inom cirkel med 25 m radie 7-8 tallar med lav på stammarna,</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,6 +2921,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2918,45 +2940,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128466272</v>
+        <v>128466264</v>
       </c>
       <c r="B22" t="n">
-        <v>92806</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462727</v>
+        <v>462644</v>
       </c>
       <c r="R22" t="n">
-        <v>6696783</v>
+        <v>6696869</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,7 +3013,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2998,7 +3023,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,6 +3037,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3025,42 +3056,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128466225</v>
+        <v>128466265</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3068,10 +3094,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462768</v>
+        <v>462675</v>
       </c>
       <c r="R23" t="n">
-        <v>6696701</v>
+        <v>6696895</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,7 +3129,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3113,12 +3139,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,6 +3153,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3145,45 +3172,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128466247</v>
+        <v>128466266</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462368</v>
+        <v>462594</v>
       </c>
       <c r="R24" t="n">
-        <v>6697278</v>
+        <v>6696982</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3215,7 +3245,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3225,7 +3255,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På 3-4 tallstammar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3234,6 +3269,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3252,32 +3288,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128466238</v>
+        <v>128466267</v>
       </c>
       <c r="B25" t="n">
-        <v>91535</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3290,10 +3326,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462777</v>
+        <v>462585</v>
       </c>
       <c r="R25" t="n">
-        <v>6696623</v>
+        <v>6696939</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3335,7 +3371,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På grenar på undertryckt gran intill tall,</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,14 +3404,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128466269</v>
+        <v>128466268</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3398,10 +3439,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462378</v>
+        <v>462386</v>
       </c>
       <c r="R26" t="n">
-        <v>6697317</v>
+        <v>6697359</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,7 +3474,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3443,7 +3484,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,14 +3511,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128466263</v>
+        <v>128466269</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3499,19 +3540,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462702</v>
+        <v>462378</v>
       </c>
       <c r="R27" t="n">
-        <v>6696765</v>
+        <v>6697317</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3543,7 +3581,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3553,12 +3591,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Inom cirkel med 25 m radie 7-8 tallar med lav på stammarna,</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3567,7 +3600,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3586,32 +3618,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128466242</v>
+        <v>128466249</v>
       </c>
       <c r="B28" t="n">
-        <v>92818</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3621,10 +3653,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462476</v>
+        <v>462756</v>
       </c>
       <c r="R28" t="n">
-        <v>6697152</v>
+        <v>6696647</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3688,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3698,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3675,7 +3707,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3694,10 +3725,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128466223</v>
+        <v>128466251</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3705,42 +3736,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462561</v>
+        <v>462497</v>
       </c>
       <c r="R29" t="n">
-        <v>6697006</v>
+        <v>6697135</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3772,7 +3795,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3782,12 +3805,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,10 +3832,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128466262</v>
+        <v>128466252</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3825,37 +3843,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462731</v>
+        <v>462485</v>
       </c>
       <c r="R30" t="n">
-        <v>6696782</v>
+        <v>6697146</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3887,7 +3902,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3897,12 +3912,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På äldre grövre tallstam.</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3911,7 +3921,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3930,10 +3939,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128466264</v>
+        <v>128466253</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,37 +3950,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462644</v>
+        <v>462421</v>
       </c>
       <c r="R31" t="n">
-        <v>6696869</v>
+        <v>6697341</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4003,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4013,12 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,7 +4028,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4046,37 +4046,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128466258</v>
+        <v>128466239</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4084,10 +4093,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462346</v>
+        <v>462507</v>
       </c>
       <c r="R32" t="n">
-        <v>6697328</v>
+        <v>6697019</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4119,7 +4128,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4129,12 +4138,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På tallstam.</t>
+          <t>Äldre stor tall med spillkråkehål.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4143,7 +4152,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4162,10 +4170,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128466233</v>
+        <v>128466223</v>
       </c>
       <c r="B33" t="n">
-        <v>91535</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4173,26 +4181,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4200,10 +4213,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462380</v>
+        <v>462561</v>
       </c>
       <c r="R33" t="n">
-        <v>6697276</v>
+        <v>6697006</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4235,7 +4248,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4245,7 +4258,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4254,7 +4272,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4273,45 +4290,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128466273</v>
+        <v>128466224</v>
       </c>
       <c r="B34" t="n">
-        <v>92806</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462356</v>
+        <v>462469</v>
       </c>
       <c r="R34" t="n">
-        <v>6697346</v>
+        <v>6697194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,7 +4368,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4353,7 +4378,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,10 +4410,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128466268</v>
+        <v>128466225</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,34 +4421,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462386</v>
+        <v>462768</v>
       </c>
       <c r="R35" t="n">
-        <v>6697359</v>
+        <v>6696701</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4450,7 +4488,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4460,7 +4498,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4487,10 +4530,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128466261</v>
+        <v>128466226</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,26 +4541,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4525,10 +4573,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462748</v>
+        <v>462534</v>
       </c>
       <c r="R36" t="n">
-        <v>6696705</v>
+        <v>6696943</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4560,7 +4608,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4570,12 +4618,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På tallstam.</t>
+          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4584,7 +4632,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4603,37 +4650,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128466275</v>
+        <v>128466227</v>
       </c>
       <c r="B37" t="n">
-        <v>92806</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4641,10 +4693,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462670</v>
+        <v>462484</v>
       </c>
       <c r="R37" t="n">
-        <v>6696759</v>
+        <v>6697200</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4676,7 +4728,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4686,7 +4738,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4695,7 +4752,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4714,10 +4770,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128466267</v>
+        <v>128466230</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4725,26 +4781,35 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4752,10 +4817,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462585</v>
+        <v>462362</v>
       </c>
       <c r="R38" t="n">
-        <v>6696939</v>
+        <v>6697282</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4787,7 +4852,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4797,12 +4862,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På grenar på undertryckt gran intill tall,</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4811,7 +4871,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4830,10 +4889,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128466252</v>
+        <v>128466231</v>
       </c>
       <c r="B39" t="n">
-        <v>78786</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4841,21 +4900,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4865,10 +4924,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462485</v>
+        <v>462657</v>
       </c>
       <c r="R39" t="n">
-        <v>6697146</v>
+        <v>6696882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4900,7 +4959,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4910,7 +4969,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4937,46 +4996,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128466277</v>
+        <v>128466232</v>
       </c>
       <c r="B40" t="n">
-        <v>96765</v>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4984,10 +5043,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462757</v>
+        <v>462418</v>
       </c>
       <c r="R40" t="n">
-        <v>6696682</v>
+        <v>6697314</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5019,7 +5078,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5029,12 +5088,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ca.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,7 +5097,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5062,37 +5115,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128466236</v>
+        <v>128466221</v>
       </c>
       <c r="B41" t="n">
-        <v>91535</v>
+        <v>5199</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5100,10 +5159,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462733</v>
+        <v>462534</v>
       </c>
       <c r="R41" t="n">
-        <v>6696654</v>
+        <v>6697251</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5135,7 +5194,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5145,7 +5204,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,57 +5232,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128466239</v>
+        <v>128466247</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>8455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462507</v>
+        <v>462368</v>
       </c>
       <c r="R42" t="n">
-        <v>6697019</v>
+        <v>6697278</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5255,7 +5302,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5265,12 +5312,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre stor tall med spillkråkehål.</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5294,6 +5336,434 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128466248</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>462651</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6696877</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128466243</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>462628</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6696967</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128466244</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>462583</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6696944</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128466245</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>462529</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6697126</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466277</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466270</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466271</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466273</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466274</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466275</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466276</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466241</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466242</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466233</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2028,6 +2088,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466235</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2139,6 +2204,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466236</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466238</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2357,6 +2432,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466222</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2473,6 +2553,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466258</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2589,6 +2674,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466260</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2705,6 +2795,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466261</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2821,6 +2916,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466262</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2937,6 +3037,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466263</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3053,6 +3158,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466264</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3169,6 +3279,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466265</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3285,6 +3400,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466266</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3401,6 +3521,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466267</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3508,6 +3633,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466268</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3615,6 +3745,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466269</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3722,6 +3857,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466249</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3829,6 +3969,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466251</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3936,6 +4081,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466252</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4043,6 +4193,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466253</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4167,6 +4322,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466239</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4287,6 +4447,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466223</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4407,6 +4572,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466224</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4527,6 +4697,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466225</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4647,6 +4822,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466226</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4767,6 +4947,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466227</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4886,6 +5071,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466230</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4993,6 +5183,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466231</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5112,6 +5307,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466232</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5229,6 +5429,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466221</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5336,6 +5541,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466247</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5443,6 +5653,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466248</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5550,6 +5765,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466243</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5657,6 +5877,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466244</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5764,8 +5989,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,48 +2328,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128466222</v>
+        <v>135618134</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>92037</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462417</v>
+        <v>462668</v>
       </c>
       <c r="R16" t="n">
-        <v>6697315</v>
+        <v>6696686</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2393,22 +2396,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,55 +2410,56 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466222</t>
+          <t>https://artportalen.se/Sighting/135618134</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128466258</v>
+        <v>135618145</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>92037</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2474,17 +2468,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462346</v>
+        <v>462676</v>
       </c>
       <c r="R17" t="n">
-        <v>6697328</v>
+        <v>6696677</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2508,27 +2502,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,65 +2523,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466258</t>
+          <t>https://artportalen.se/Sighting/135618145</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128466260</v>
+        <v>128466222</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462377</v>
+        <v>462417</v>
       </c>
       <c r="R18" t="n">
-        <v>6697267</v>
+        <v>6697315</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2610,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2620,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,7 +2629,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2676,13 +2646,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466260</t>
+          <t>https://artportalen.se/Sighting/128466222</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128466261</v>
+        <v>128466258</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2720,10 +2690,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462748</v>
+        <v>462346</v>
       </c>
       <c r="R19" t="n">
-        <v>6696705</v>
+        <v>6697328</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2725,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2765,7 +2735,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2797,13 +2767,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466261</t>
+          <t>https://artportalen.se/Sighting/128466258</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128466262</v>
+        <v>128466260</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2841,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462731</v>
+        <v>462377</v>
       </c>
       <c r="R20" t="n">
-        <v>6696782</v>
+        <v>6697267</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2876,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2886,12 +2856,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På äldre grövre tallstam.</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2918,13 +2888,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466262</t>
+          <t>https://artportalen.se/Sighting/128466260</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128466263</v>
+        <v>128466261</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2962,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462702</v>
+        <v>462748</v>
       </c>
       <c r="R21" t="n">
-        <v>6696765</v>
+        <v>6696705</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2997,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3007,12 +2977,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Inom cirkel med 25 m radie 7-8 tallar med lav på stammarna,</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,13 +3009,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466263</t>
+          <t>https://artportalen.se/Sighting/128466261</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128466264</v>
+        <v>128466262</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -3083,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462644</v>
+        <v>462731</v>
       </c>
       <c r="R22" t="n">
-        <v>6696869</v>
+        <v>6696782</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3118,7 +3088,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3128,12 +3098,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På tallstam</t>
+          <t>På äldre grövre tallstam.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3160,13 +3130,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466264</t>
+          <t>https://artportalen.se/Sighting/128466262</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128466265</v>
+        <v>128466263</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3204,10 +3174,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462675</v>
+        <v>462702</v>
       </c>
       <c r="R23" t="n">
-        <v>6696895</v>
+        <v>6696765</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3239,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3249,12 +3219,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På tallstam.</t>
+          <t>Inom cirkel med 25 m radie 7-8 tallar med lav på stammarna,</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3281,13 +3251,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466265</t>
+          <t>https://artportalen.se/Sighting/128466263</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128466266</v>
+        <v>128466264</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3325,10 +3295,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462594</v>
+        <v>462644</v>
       </c>
       <c r="R24" t="n">
-        <v>6696982</v>
+        <v>6696869</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3360,7 +3330,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3370,12 +3340,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På 3-4 tallstammar.</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3402,13 +3372,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466266</t>
+          <t>https://artportalen.se/Sighting/128466264</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128466267</v>
+        <v>128466265</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3446,10 +3416,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462585</v>
+        <v>462675</v>
       </c>
       <c r="R25" t="n">
-        <v>6696939</v>
+        <v>6696895</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3481,7 +3451,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3491,12 +3461,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På grenar på undertryckt gran intill tall,</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3523,13 +3493,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466267</t>
+          <t>https://artportalen.se/Sighting/128466265</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128466268</v>
+        <v>128466266</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3558,16 +3528,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462386</v>
+        <v>462594</v>
       </c>
       <c r="R26" t="n">
-        <v>6697359</v>
+        <v>6696982</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3599,7 +3572,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3609,7 +3582,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På 3-4 tallstammar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3618,6 +3596,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3635,13 +3614,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466268</t>
+          <t>https://artportalen.se/Sighting/128466266</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128466269</v>
+        <v>128466267</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3670,16 +3649,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462378</v>
+        <v>462585</v>
       </c>
       <c r="R27" t="n">
-        <v>6697317</v>
+        <v>6696939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3711,7 +3693,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,7 +3703,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På grenar på undertryckt gran intill tall,</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,6 +3717,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3747,38 +3735,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466269</t>
+          <t>https://artportalen.se/Sighting/128466267</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128466249</v>
+        <v>128466268</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3788,10 +3776,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462756</v>
+        <v>462386</v>
       </c>
       <c r="R28" t="n">
-        <v>6696647</v>
+        <v>6697359</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3811,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3821,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3859,38 +3847,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466249</t>
+          <t>https://artportalen.se/Sighting/128466268</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128466251</v>
+        <v>128466269</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3900,10 +3888,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462497</v>
+        <v>462378</v>
       </c>
       <c r="R29" t="n">
-        <v>6697135</v>
+        <v>6697317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3935,7 +3923,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3933,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3971,13 +3959,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466251</t>
+          <t>https://artportalen.se/Sighting/128466269</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128466252</v>
+        <v>128466249</v>
       </c>
       <c r="B30" t="n">
         <v>79084</v>
@@ -4012,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462485</v>
+        <v>462756</v>
       </c>
       <c r="R30" t="n">
-        <v>6697146</v>
+        <v>6696647</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4047,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4083,13 +4071,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466252</t>
+          <t>https://artportalen.se/Sighting/128466249</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128466253</v>
+        <v>128466251</v>
       </c>
       <c r="B31" t="n">
         <v>79084</v>
@@ -4124,10 +4112,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462421</v>
+        <v>462497</v>
       </c>
       <c r="R31" t="n">
-        <v>6697341</v>
+        <v>6697135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4159,7 +4147,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4169,7 +4157,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4195,63 +4183,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466253</t>
+          <t>https://artportalen.se/Sighting/128466251</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128466239</v>
+        <v>128466252</v>
       </c>
       <c r="B32" t="n">
-        <v>57950</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462507</v>
+        <v>462485</v>
       </c>
       <c r="R32" t="n">
-        <v>6697019</v>
+        <v>6697146</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4283,7 +4259,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4293,12 +4269,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre stor tall med spillkråkehål.</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4324,16 +4295,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466239</t>
+          <t>https://artportalen.se/Sighting/128466252</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128466223</v>
+        <v>128466253</v>
       </c>
       <c r="B33" t="n">
-        <v>57953</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4341,42 +4312,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462561</v>
+        <v>462421</v>
       </c>
       <c r="R33" t="n">
-        <v>6697006</v>
+        <v>6697341</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4371,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,12 +4381,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4449,33 +4407,33 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466223</t>
+          <t>https://artportalen.se/Sighting/128466253</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128466224</v>
+        <v>128466239</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4483,12 +4441,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4498,10 +4460,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462469</v>
+        <v>462507</v>
       </c>
       <c r="R34" t="n">
-        <v>6697194</v>
+        <v>6697019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4533,7 +4495,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4543,12 +4505,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Äldre stor tall med spillkråkehål.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4574,33 +4536,33 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466224</t>
+          <t>https://artportalen.se/Sighting/128466239</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128466225</v>
+        <v>135618319</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4613,23 +4575,23 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462768</v>
+        <v>462685</v>
       </c>
       <c r="R35" t="n">
-        <v>6696701</v>
+        <v>6696752</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4653,27 +4615,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>i äldre asp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4688,24 +4640,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466225</t>
+          <t>https://artportalen.se/Sighting/135618319</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128466226</v>
+        <v>128466223</v>
       </c>
       <c r="B36" t="n">
         <v>57953</v>
@@ -4738,7 +4690,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4748,10 +4700,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462534</v>
+        <v>462561</v>
       </c>
       <c r="R36" t="n">
-        <v>6696943</v>
+        <v>6697006</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4783,7 +4735,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4793,12 +4745,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4824,13 +4776,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466226</t>
+          <t>https://artportalen.se/Sighting/128466223</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128466227</v>
+        <v>128466224</v>
       </c>
       <c r="B37" t="n">
         <v>57953</v>
@@ -4873,10 +4825,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462484</v>
+        <v>462469</v>
       </c>
       <c r="R37" t="n">
-        <v>6697200</v>
+        <v>6697194</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4908,7 +4860,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4918,12 +4870,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4949,16 +4901,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466227</t>
+          <t>https://artportalen.se/Sighting/128466224</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128466230</v>
+        <v>128466225</v>
       </c>
       <c r="B38" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,33 +4918,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5002,10 +4950,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462362</v>
+        <v>462768</v>
       </c>
       <c r="R38" t="n">
-        <v>6697282</v>
+        <v>6696701</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5037,7 +4985,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5047,7 +4995,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5073,16 +5026,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466230</t>
+          <t>https://artportalen.se/Sighting/128466225</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128466231</v>
+        <v>128466226</v>
       </c>
       <c r="B39" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5090,34 +5043,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462657</v>
+        <v>462534</v>
       </c>
       <c r="R39" t="n">
-        <v>6696882</v>
+        <v>6696943</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5149,7 +5110,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5159,7 +5120,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5185,16 +5151,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466231</t>
+          <t>https://artportalen.se/Sighting/128466226</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128466232</v>
+        <v>128466227</v>
       </c>
       <c r="B40" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,33 +5168,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5238,10 +5200,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462418</v>
+        <v>462484</v>
       </c>
       <c r="R40" t="n">
-        <v>6697314</v>
+        <v>6697200</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5273,7 +5235,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5283,7 +5245,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5309,33 +5276,33 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466232</t>
+          <t>https://artportalen.se/Sighting/128466227</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128466221</v>
+        <v>135618199</v>
       </c>
       <c r="B41" t="n">
-        <v>5199</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5344,28 +5311,27 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462534</v>
+        <v>462720</v>
       </c>
       <c r="R41" t="n">
-        <v>6697251</v>
+        <v>6696663</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5389,22 +5355,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5413,72 +5374,79 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466221</t>
+          <t>https://artportalen.se/Sighting/135618199</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128466247</v>
+        <v>135618210</v>
       </c>
       <c r="B42" t="n">
-        <v>8455</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462368</v>
+        <v>462664</v>
       </c>
       <c r="R42" t="n">
-        <v>6697278</v>
+        <v>6696677</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5502,22 +5470,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:50</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:50</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5532,65 +5495,73 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466247</t>
+          <t>https://artportalen.se/Sighting/135618210</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128466248</v>
+        <v>135618226</v>
       </c>
       <c r="B43" t="n">
-        <v>8455</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462651</v>
+        <v>462624</v>
       </c>
       <c r="R43" t="n">
-        <v>6696877</v>
+        <v>6696720</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5614,22 +5585,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5644,27 +5610,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466248</t>
+          <t>https://artportalen.se/Sighting/135618226</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128466243</v>
+        <v>135618241</v>
       </c>
       <c r="B44" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5672,37 +5638,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462628</v>
+        <v>462640</v>
       </c>
       <c r="R44" t="n">
-        <v>6696967</v>
+        <v>6696727</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5726,22 +5700,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5756,27 +5725,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466243</t>
+          <t>https://artportalen.se/Sighting/135618241</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128466244</v>
+        <v>135618331</v>
       </c>
       <c r="B45" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5784,37 +5753,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462583</v>
+        <v>462724</v>
       </c>
       <c r="R45" t="n">
-        <v>6696944</v>
+        <v>6696755</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5838,22 +5815,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5868,27 +5840,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466244</t>
+          <t>https://artportalen.se/Sighting/135618331</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128466245</v>
+        <v>135618395</v>
       </c>
       <c r="B46" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5896,37 +5868,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462529</v>
+        <v>462569</v>
       </c>
       <c r="R46" t="n">
-        <v>6697126</v>
+        <v>6696848</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5950,22 +5930,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5980,16 +5955,1403 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135618395</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135618401</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Länsmansberget, Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>462589</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6696851</v>
+      </c>
+      <c r="S47" t="n">
+        <v>50</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ringhavk på tall</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135618401</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135618420</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Länsmansberget, Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>462607</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6697017</v>
+      </c>
+      <c r="S48" t="n">
+        <v>50</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135618420</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135618432</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Länsmansberget, Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>462608</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6697000</v>
+      </c>
+      <c r="S49" t="n">
+        <v>50</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135618432</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128466230</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>462362</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6697282</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466230</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128466231</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>462657</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6696882</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466231</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128466232</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>462418</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6697314</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466232</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128466221</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>462534</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6697251</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466221</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128466247</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>462368</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6697278</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466247</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128466248</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>462651</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6696877</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466248</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128466243</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>462628</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6696967</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466243</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128466244</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>462583</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6696944</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466244</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128466245</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>462529</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6697126</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128466245</t>
         </is>
@@ -6042,6 +7404,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -2331,7 +2331,7 @@
         <v>135618134</v>
       </c>
       <c r="B16" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>135618145</v>
       </c>
       <c r="B17" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,48 +2328,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128466222</v>
+        <v>135618134</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462417</v>
+        <v>462668</v>
       </c>
       <c r="R16" t="n">
-        <v>6697315</v>
+        <v>6696686</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2393,22 +2396,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,55 +2410,56 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466222</t>
+          <t>https://artportalen.se/Sighting/135618134</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128466258</v>
+        <v>135618145</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>92069</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2474,17 +2468,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462346</v>
+        <v>462676</v>
       </c>
       <c r="R17" t="n">
-        <v>6697328</v>
+        <v>6696677</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2508,27 +2502,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,65 +2523,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466258</t>
+          <t>https://artportalen.se/Sighting/135618145</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128466260</v>
+        <v>128466222</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462377</v>
+        <v>462417</v>
       </c>
       <c r="R18" t="n">
-        <v>6697267</v>
+        <v>6697315</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2610,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2620,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,7 +2629,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2676,13 +2646,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466260</t>
+          <t>https://artportalen.se/Sighting/128466222</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128466261</v>
+        <v>128466258</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2720,10 +2690,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462748</v>
+        <v>462346</v>
       </c>
       <c r="R19" t="n">
-        <v>6696705</v>
+        <v>6697328</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2725,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2765,7 +2735,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2797,13 +2767,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466261</t>
+          <t>https://artportalen.se/Sighting/128466258</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128466262</v>
+        <v>128466260</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2841,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462731</v>
+        <v>462377</v>
       </c>
       <c r="R20" t="n">
-        <v>6696782</v>
+        <v>6697267</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2876,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2886,12 +2856,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På äldre grövre tallstam.</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2918,13 +2888,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466262</t>
+          <t>https://artportalen.se/Sighting/128466260</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128466263</v>
+        <v>128466261</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2962,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462702</v>
+        <v>462748</v>
       </c>
       <c r="R21" t="n">
-        <v>6696765</v>
+        <v>6696705</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2997,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3007,12 +2977,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Inom cirkel med 25 m radie 7-8 tallar med lav på stammarna,</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,13 +3009,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466263</t>
+          <t>https://artportalen.se/Sighting/128466261</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128466264</v>
+        <v>128466262</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -3083,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462644</v>
+        <v>462731</v>
       </c>
       <c r="R22" t="n">
-        <v>6696869</v>
+        <v>6696782</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3118,7 +3088,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3128,12 +3098,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På tallstam</t>
+          <t>På äldre grövre tallstam.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3160,13 +3130,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466264</t>
+          <t>https://artportalen.se/Sighting/128466262</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128466265</v>
+        <v>128466263</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3204,10 +3174,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462675</v>
+        <v>462702</v>
       </c>
       <c r="R23" t="n">
-        <v>6696895</v>
+        <v>6696765</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3239,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3249,12 +3219,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På tallstam.</t>
+          <t>Inom cirkel med 25 m radie 7-8 tallar med lav på stammarna,</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3281,13 +3251,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466265</t>
+          <t>https://artportalen.se/Sighting/128466263</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128466266</v>
+        <v>128466264</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3325,10 +3295,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462594</v>
+        <v>462644</v>
       </c>
       <c r="R24" t="n">
-        <v>6696982</v>
+        <v>6696869</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3360,7 +3330,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3370,12 +3340,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På 3-4 tallstammar.</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3402,13 +3372,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466266</t>
+          <t>https://artportalen.se/Sighting/128466264</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128466267</v>
+        <v>128466265</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3446,10 +3416,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462585</v>
+        <v>462675</v>
       </c>
       <c r="R25" t="n">
-        <v>6696939</v>
+        <v>6696895</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3481,7 +3451,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3491,12 +3461,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På grenar på undertryckt gran intill tall,</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3523,13 +3493,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466267</t>
+          <t>https://artportalen.se/Sighting/128466265</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128466268</v>
+        <v>128466266</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3558,16 +3528,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462386</v>
+        <v>462594</v>
       </c>
       <c r="R26" t="n">
-        <v>6697359</v>
+        <v>6696982</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3599,7 +3572,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3609,7 +3582,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På 3-4 tallstammar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3618,6 +3596,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3635,13 +3614,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466268</t>
+          <t>https://artportalen.se/Sighting/128466266</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128466269</v>
+        <v>128466267</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3670,16 +3649,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462378</v>
+        <v>462585</v>
       </c>
       <c r="R27" t="n">
-        <v>6697317</v>
+        <v>6696939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3711,7 +3693,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,7 +3703,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På grenar på undertryckt gran intill tall,</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,6 +3717,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3747,38 +3735,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466269</t>
+          <t>https://artportalen.se/Sighting/128466267</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128466249</v>
+        <v>128466268</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3788,10 +3776,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462756</v>
+        <v>462386</v>
       </c>
       <c r="R28" t="n">
-        <v>6696647</v>
+        <v>6697359</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3811,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3821,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3859,38 +3847,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466249</t>
+          <t>https://artportalen.se/Sighting/128466268</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128466251</v>
+        <v>128466269</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3900,10 +3888,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462497</v>
+        <v>462378</v>
       </c>
       <c r="R29" t="n">
-        <v>6697135</v>
+        <v>6697317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3935,7 +3923,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3933,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3971,13 +3959,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466251</t>
+          <t>https://artportalen.se/Sighting/128466269</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128466252</v>
+        <v>128466249</v>
       </c>
       <c r="B30" t="n">
         <v>79084</v>
@@ -4012,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462485</v>
+        <v>462756</v>
       </c>
       <c r="R30" t="n">
-        <v>6697146</v>
+        <v>6696647</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4047,7 +4035,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,7 +4045,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4083,13 +4071,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466252</t>
+          <t>https://artportalen.se/Sighting/128466249</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128466253</v>
+        <v>128466251</v>
       </c>
       <c r="B31" t="n">
         <v>79084</v>
@@ -4124,10 +4112,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462421</v>
+        <v>462497</v>
       </c>
       <c r="R31" t="n">
-        <v>6697341</v>
+        <v>6697135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4159,7 +4147,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4169,7 +4157,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4195,63 +4183,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466253</t>
+          <t>https://artportalen.se/Sighting/128466251</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128466239</v>
+        <v>128466252</v>
       </c>
       <c r="B32" t="n">
-        <v>57950</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462507</v>
+        <v>462485</v>
       </c>
       <c r="R32" t="n">
-        <v>6697019</v>
+        <v>6697146</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4283,7 +4259,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4293,12 +4269,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre stor tall med spillkråkehål.</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4324,16 +4295,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466239</t>
+          <t>https://artportalen.se/Sighting/128466252</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128466223</v>
+        <v>128466253</v>
       </c>
       <c r="B33" t="n">
-        <v>57953</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4341,42 +4312,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462561</v>
+        <v>462421</v>
       </c>
       <c r="R33" t="n">
-        <v>6697006</v>
+        <v>6697341</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4408,7 +4371,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4418,12 +4381,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4449,33 +4407,33 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466223</t>
+          <t>https://artportalen.se/Sighting/128466253</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128466224</v>
+        <v>128466239</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4483,12 +4441,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4498,10 +4460,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462469</v>
+        <v>462507</v>
       </c>
       <c r="R34" t="n">
-        <v>6697194</v>
+        <v>6697019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4533,7 +4495,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4543,12 +4505,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Äldre stor tall med spillkråkehål.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4574,33 +4536,33 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466224</t>
+          <t>https://artportalen.se/Sighting/128466239</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128466225</v>
+        <v>135618319</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4613,23 +4575,23 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462768</v>
+        <v>462685</v>
       </c>
       <c r="R35" t="n">
-        <v>6696701</v>
+        <v>6696752</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4653,27 +4615,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>i äldre asp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4688,24 +4640,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466225</t>
+          <t>https://artportalen.se/Sighting/135618319</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128466226</v>
+        <v>128466223</v>
       </c>
       <c r="B36" t="n">
         <v>57953</v>
@@ -4738,7 +4690,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4748,10 +4700,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462534</v>
+        <v>462561</v>
       </c>
       <c r="R36" t="n">
-        <v>6696943</v>
+        <v>6697006</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4783,7 +4735,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4793,12 +4745,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4824,13 +4776,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466226</t>
+          <t>https://artportalen.se/Sighting/128466223</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128466227</v>
+        <v>128466224</v>
       </c>
       <c r="B37" t="n">
         <v>57953</v>
@@ -4873,10 +4825,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462484</v>
+        <v>462469</v>
       </c>
       <c r="R37" t="n">
-        <v>6697200</v>
+        <v>6697194</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4908,7 +4860,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4918,12 +4870,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4949,16 +4901,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466227</t>
+          <t>https://artportalen.se/Sighting/128466224</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128466230</v>
+        <v>128466225</v>
       </c>
       <c r="B38" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,33 +4918,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5002,10 +4950,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462362</v>
+        <v>462768</v>
       </c>
       <c r="R38" t="n">
-        <v>6697282</v>
+        <v>6696701</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5037,7 +4985,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5047,7 +4995,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5073,16 +5026,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466230</t>
+          <t>https://artportalen.se/Sighting/128466225</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128466231</v>
+        <v>128466226</v>
       </c>
       <c r="B39" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5090,34 +5043,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462657</v>
+        <v>462534</v>
       </c>
       <c r="R39" t="n">
-        <v>6696882</v>
+        <v>6696943</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5149,7 +5110,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5159,7 +5120,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5185,16 +5151,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466231</t>
+          <t>https://artportalen.se/Sighting/128466226</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128466232</v>
+        <v>128466227</v>
       </c>
       <c r="B40" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,33 +5168,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5238,10 +5200,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462418</v>
+        <v>462484</v>
       </c>
       <c r="R40" t="n">
-        <v>6697314</v>
+        <v>6697200</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5273,7 +5235,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5283,7 +5245,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5309,33 +5276,33 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466232</t>
+          <t>https://artportalen.se/Sighting/128466227</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128466221</v>
+        <v>135618199</v>
       </c>
       <c r="B41" t="n">
-        <v>5199</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5344,28 +5311,27 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462534</v>
+        <v>462720</v>
       </c>
       <c r="R41" t="n">
-        <v>6697251</v>
+        <v>6696663</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5389,22 +5355,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5413,72 +5374,79 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466221</t>
+          <t>https://artportalen.se/Sighting/135618199</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128466247</v>
+        <v>135618210</v>
       </c>
       <c r="B42" t="n">
-        <v>8455</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462368</v>
+        <v>462664</v>
       </c>
       <c r="R42" t="n">
-        <v>6697278</v>
+        <v>6696677</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5502,22 +5470,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:50</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:50</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5532,65 +5495,73 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466247</t>
+          <t>https://artportalen.se/Sighting/135618210</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128466248</v>
+        <v>135618226</v>
       </c>
       <c r="B43" t="n">
-        <v>8455</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462651</v>
+        <v>462624</v>
       </c>
       <c r="R43" t="n">
-        <v>6696877</v>
+        <v>6696720</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5614,22 +5585,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5644,27 +5610,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466248</t>
+          <t>https://artportalen.se/Sighting/135618226</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128466243</v>
+        <v>135618241</v>
       </c>
       <c r="B44" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5672,37 +5638,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462628</v>
+        <v>462640</v>
       </c>
       <c r="R44" t="n">
-        <v>6696967</v>
+        <v>6696727</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5726,22 +5700,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5756,27 +5725,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466243</t>
+          <t>https://artportalen.se/Sighting/135618241</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128466244</v>
+        <v>135618331</v>
       </c>
       <c r="B45" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5784,37 +5753,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462583</v>
+        <v>462724</v>
       </c>
       <c r="R45" t="n">
-        <v>6696944</v>
+        <v>6696755</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5838,22 +5815,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5868,27 +5840,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466244</t>
+          <t>https://artportalen.se/Sighting/135618331</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128466245</v>
+        <v>135618395</v>
       </c>
       <c r="B46" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5896,37 +5868,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462529</v>
+        <v>462569</v>
       </c>
       <c r="R46" t="n">
-        <v>6697126</v>
+        <v>6696848</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5950,22 +5930,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5980,16 +5955,1403 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135618395</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135618401</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Länsmansberget, Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>462589</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6696851</v>
+      </c>
+      <c r="S47" t="n">
+        <v>50</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ringhavk på tall</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135618401</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135618420</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Länsmansberget, Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>462607</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6697017</v>
+      </c>
+      <c r="S48" t="n">
+        <v>50</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135618420</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135618432</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Länsmansberget, Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>462608</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6697000</v>
+      </c>
+      <c r="S49" t="n">
+        <v>50</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135618432</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128466230</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>462362</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6697282</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466230</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128466231</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>462657</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6696882</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466231</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128466232</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>462418</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6697314</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466232</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128466221</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>462534</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6697251</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466221</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128466247</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>462368</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6697278</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466247</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128466248</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>462651</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6696877</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466248</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128466243</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>462628</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6696967</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466243</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128466244</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>462583</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6696944</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466244</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128466245</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>462529</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6697126</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128466245</t>
         </is>
@@ -6042,6 +7404,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -2331,7 +2331,7 @@
         <v>135618134</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>135618145</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -2331,7 +2331,7 @@
         <v>135618134</v>
       </c>
       <c r="B16" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>135618145</v>
       </c>
       <c r="B17" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>135618319</v>
       </c>
       <c r="B35" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>135618199</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>135618210</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>135618226</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>135618241</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>135618331</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>135618395</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>135618401</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>135618420</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>135618432</v>
       </c>
       <c r="B49" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -2331,7 +2331,7 @@
         <v>135618134</v>
       </c>
       <c r="B16" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>135618145</v>
       </c>
       <c r="B17" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ58"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1627,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128466241</v>
+        <v>136208958</v>
       </c>
       <c r="B10" t="n">
-        <v>93209</v>
+        <v>93364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,21 +1638,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1669,17 +1669,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462466</v>
+        <v>462294</v>
       </c>
       <c r="R10" t="n">
-        <v>6697178</v>
+        <v>6697190</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,22 +1703,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,24 +1724,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466241</t>
+          <t>https://artportalen.se/Sighting/136208958</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128466242</v>
+        <v>128466241</v>
       </c>
       <c r="B11" t="n">
         <v>93209</v>
@@ -1779,17 +1769,28 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462476</v>
+        <v>462466</v>
       </c>
       <c r="R11" t="n">
-        <v>6697152</v>
+        <v>6697178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1831,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,16 +1859,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466242</t>
+          <t>https://artportalen.se/Sighting/128466241</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128466233</v>
+        <v>128466242</v>
       </c>
       <c r="B12" t="n">
-        <v>91930</v>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,37 +1876,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462380</v>
+        <v>462476</v>
       </c>
       <c r="R12" t="n">
-        <v>6697276</v>
+        <v>6697152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,7 +1935,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,7 +1945,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,13 +1972,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466233</t>
+          <t>https://artportalen.se/Sighting/128466242</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128466235</v>
+        <v>128466233</v>
       </c>
       <c r="B13" t="n">
         <v>91930</v>
@@ -2018,10 +2016,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462540</v>
+        <v>462380</v>
       </c>
       <c r="R13" t="n">
-        <v>6696867</v>
+        <v>6697276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,7 +2061,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,13 +2088,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466235</t>
+          <t>https://artportalen.se/Sighting/128466233</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128466236</v>
+        <v>128466235</v>
       </c>
       <c r="B14" t="n">
         <v>91930</v>
@@ -2134,10 +2132,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462733</v>
+        <v>462540</v>
       </c>
       <c r="R14" t="n">
-        <v>6696654</v>
+        <v>6696867</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2179,7 +2177,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,13 +2204,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466236</t>
+          <t>https://artportalen.se/Sighting/128466235</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128466238</v>
+        <v>128466236</v>
       </c>
       <c r="B15" t="n">
         <v>91930</v>
@@ -2250,10 +2248,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462777</v>
+        <v>462733</v>
       </c>
       <c r="R15" t="n">
-        <v>6696623</v>
+        <v>6696654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,7 +2283,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2295,7 +2293,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2322,16 +2320,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466238</t>
+          <t>https://artportalen.se/Sighting/128466236</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135618134</v>
+        <v>128466238</v>
       </c>
       <c r="B16" t="n">
-        <v>92086</v>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,17 +2360,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Länsmansberget, Väster, Dlr</t>
+          <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462668</v>
+        <v>462777</v>
       </c>
       <c r="R16" t="n">
-        <v>6696686</v>
+        <v>6696623</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2396,12 +2394,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,27 +2425,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618134</t>
+          <t>https://artportalen.se/Sighting/128466238</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135618145</v>
+        <v>135618134</v>
       </c>
       <c r="B17" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,10 +2480,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462676</v>
+        <v>462668</v>
       </c>
       <c r="R17" t="n">
-        <v>6696677</v>
+        <v>6696686</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2534,54 +2542,57 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618145</t>
+          <t>https://artportalen.se/Sighting/135618134</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128466222</v>
+        <v>135618145</v>
       </c>
       <c r="B18" t="n">
-        <v>91872</v>
+        <v>92087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462417</v>
+        <v>462676</v>
       </c>
       <c r="R18" t="n">
-        <v>6697315</v>
+        <v>6696677</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2605,22 +2616,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,71 +2630,69 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466222</t>
+          <t>https://artportalen.se/Sighting/135618145</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128466258</v>
+        <v>128466222</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462346</v>
+        <v>462417</v>
       </c>
       <c r="R19" t="n">
-        <v>6697328</v>
+        <v>6697315</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2725,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2735,12 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,7 +2743,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2767,13 +2760,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466258</t>
+          <t>https://artportalen.se/Sighting/128466222</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128466260</v>
+        <v>128466258</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2811,10 +2804,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462377</v>
+        <v>462346</v>
       </c>
       <c r="R20" t="n">
-        <v>6697267</v>
+        <v>6697328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,7 +2839,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,7 +2849,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2888,13 +2881,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466260</t>
+          <t>https://artportalen.se/Sighting/128466258</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128466261</v>
+        <v>128466260</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2932,10 +2925,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462748</v>
+        <v>462377</v>
       </c>
       <c r="R21" t="n">
-        <v>6696705</v>
+        <v>6697267</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,7 +2960,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,7 +2970,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3009,13 +3002,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466261</t>
+          <t>https://artportalen.se/Sighting/128466260</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128466262</v>
+        <v>128466261</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -3053,10 +3046,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462731</v>
+        <v>462748</v>
       </c>
       <c r="R22" t="n">
-        <v>6696782</v>
+        <v>6696705</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3088,7 +3081,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3098,12 +3091,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På äldre grövre tallstam.</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3130,13 +3123,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466262</t>
+          <t>https://artportalen.se/Sighting/128466261</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128466263</v>
+        <v>128466262</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3174,10 +3167,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462702</v>
+        <v>462731</v>
       </c>
       <c r="R23" t="n">
-        <v>6696765</v>
+        <v>6696782</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3209,7 +3202,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3219,12 +3212,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Inom cirkel med 25 m radie 7-8 tallar med lav på stammarna,</t>
+          <t>På äldre grövre tallstam.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,13 +3244,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466263</t>
+          <t>https://artportalen.se/Sighting/128466262</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128466264</v>
+        <v>128466263</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3295,10 +3288,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462644</v>
+        <v>462702</v>
       </c>
       <c r="R24" t="n">
-        <v>6696869</v>
+        <v>6696765</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3330,7 +3323,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3340,12 +3333,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På tallstam</t>
+          <t>Inom cirkel med 25 m radie 7-8 tallar med lav på stammarna,</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3372,13 +3365,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466264</t>
+          <t>https://artportalen.se/Sighting/128466263</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128466265</v>
+        <v>128466264</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3416,10 +3409,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462675</v>
+        <v>462644</v>
       </c>
       <c r="R25" t="n">
-        <v>6696895</v>
+        <v>6696869</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3451,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3461,12 +3454,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På tallstam.</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3493,13 +3486,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466265</t>
+          <t>https://artportalen.se/Sighting/128466264</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128466266</v>
+        <v>128466265</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3537,10 +3530,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462594</v>
+        <v>462675</v>
       </c>
       <c r="R26" t="n">
-        <v>6696982</v>
+        <v>6696895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3572,7 +3565,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3582,12 +3575,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På 3-4 tallstammar.</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3614,13 +3607,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466266</t>
+          <t>https://artportalen.se/Sighting/128466265</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128466267</v>
+        <v>128466266</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3658,10 +3651,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462585</v>
+        <v>462594</v>
       </c>
       <c r="R27" t="n">
-        <v>6696939</v>
+        <v>6696982</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3693,7 +3686,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3703,12 +3696,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På grenar på undertryckt gran intill tall,</t>
+          <t>På 3-4 tallstammar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3735,13 +3728,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466267</t>
+          <t>https://artportalen.se/Sighting/128466266</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128466268</v>
+        <v>128466267</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3770,16 +3763,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462386</v>
+        <v>462585</v>
       </c>
       <c r="R28" t="n">
-        <v>6697359</v>
+        <v>6696939</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3811,7 +3807,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3821,7 +3817,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På grenar på undertryckt gran intill tall,</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3830,6 +3831,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3847,13 +3849,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466268</t>
+          <t>https://artportalen.se/Sighting/128466267</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128466269</v>
+        <v>128466268</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3888,10 +3890,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462378</v>
+        <v>462386</v>
       </c>
       <c r="R29" t="n">
-        <v>6697317</v>
+        <v>6697359</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3923,7 +3925,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3933,7 +3935,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3959,38 +3961,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466269</t>
+          <t>https://artportalen.se/Sighting/128466268</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128466249</v>
+        <v>128466269</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4000,10 +4002,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462756</v>
+        <v>462378</v>
       </c>
       <c r="R30" t="n">
-        <v>6696647</v>
+        <v>6697317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4035,7 +4037,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4047,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4071,13 +4073,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466249</t>
+          <t>https://artportalen.se/Sighting/128466269</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128466251</v>
+        <v>128466249</v>
       </c>
       <c r="B31" t="n">
         <v>79084</v>
@@ -4112,10 +4114,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462497</v>
+        <v>462756</v>
       </c>
       <c r="R31" t="n">
-        <v>6697135</v>
+        <v>6696647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4147,7 +4149,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4157,7 +4159,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4183,13 +4185,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466251</t>
+          <t>https://artportalen.se/Sighting/128466249</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128466252</v>
+        <v>128466251</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -4224,10 +4226,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462485</v>
+        <v>462497</v>
       </c>
       <c r="R32" t="n">
-        <v>6697146</v>
+        <v>6697135</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4259,7 +4261,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4269,7 +4271,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4295,13 +4297,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466252</t>
+          <t>https://artportalen.se/Sighting/128466251</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128466253</v>
+        <v>128466252</v>
       </c>
       <c r="B33" t="n">
         <v>79084</v>
@@ -4336,10 +4338,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462421</v>
+        <v>462485</v>
       </c>
       <c r="R33" t="n">
-        <v>6697341</v>
+        <v>6697146</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4371,7 +4373,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4381,7 +4383,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4407,63 +4409,51 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466253</t>
+          <t>https://artportalen.se/Sighting/128466252</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128466239</v>
+        <v>128466253</v>
       </c>
       <c r="B34" t="n">
-        <v>57950</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462507</v>
+        <v>462421</v>
       </c>
       <c r="R34" t="n">
-        <v>6697019</v>
+        <v>6697341</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4495,7 +4485,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4505,12 +4495,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre stor tall med spillkråkehål.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4536,16 +4521,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466239</t>
+          <t>https://artportalen.se/Sighting/128466253</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135618319</v>
+        <v>128466239</v>
       </c>
       <c r="B35" t="n">
-        <v>57979</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,7 +4555,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -4581,17 +4570,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Länsmansberget, Väster, Dlr</t>
+          <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462685</v>
+        <v>462507</v>
       </c>
       <c r="R35" t="n">
-        <v>6696752</v>
+        <v>6697019</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4615,17 +4604,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>i äldre asp</t>
+          <t>Äldre stor tall med spillkråkehål.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4640,44 +4639,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618319</t>
+          <t>https://artportalen.se/Sighting/128466239</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128466223</v>
+        <v>135618319</v>
       </c>
       <c r="B36" t="n">
-        <v>57953</v>
+        <v>57979</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4690,23 +4689,23 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462561</v>
+        <v>462685</v>
       </c>
       <c r="R36" t="n">
-        <v>6697006</v>
+        <v>6696752</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4730,27 +4729,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>i äldre asp</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4765,44 +4754,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466223</t>
+          <t>https://artportalen.se/Sighting/135618319</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128466224</v>
+        <v>136208896</v>
       </c>
       <c r="B37" t="n">
-        <v>57953</v>
+        <v>57979</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4815,23 +4804,23 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462469</v>
+        <v>462490</v>
       </c>
       <c r="R37" t="n">
-        <v>6697194</v>
+        <v>6697013</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4855,27 +4844,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4890,24 +4869,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466224</t>
+          <t>https://artportalen.se/Sighting/136208896</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128466225</v>
+        <v>128466223</v>
       </c>
       <c r="B38" t="n">
         <v>57953</v>
@@ -4950,10 +4929,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462768</v>
+        <v>462561</v>
       </c>
       <c r="R38" t="n">
-        <v>6696701</v>
+        <v>6697006</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4985,7 +4964,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4995,12 +4974,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5026,13 +5005,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466225</t>
+          <t>https://artportalen.se/Sighting/128466223</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128466226</v>
+        <v>128466224</v>
       </c>
       <c r="B39" t="n">
         <v>57953</v>
@@ -5065,7 +5044,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5075,10 +5054,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462534</v>
+        <v>462469</v>
       </c>
       <c r="R39" t="n">
-        <v>6696943</v>
+        <v>6697194</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5110,7 +5089,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5120,12 +5099,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5151,13 +5130,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466226</t>
+          <t>https://artportalen.se/Sighting/128466224</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128466227</v>
+        <v>128466225</v>
       </c>
       <c r="B40" t="n">
         <v>57953</v>
@@ -5200,10 +5179,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462484</v>
+        <v>462768</v>
       </c>
       <c r="R40" t="n">
-        <v>6697200</v>
+        <v>6696701</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5235,7 +5214,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5245,12 +5224,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5276,16 +5255,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466227</t>
+          <t>https://artportalen.se/Sighting/128466225</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135618199</v>
+        <v>128466226</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5315,23 +5294,23 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Länsmansberget, Väster, Dlr</t>
+          <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462720</v>
+        <v>462534</v>
       </c>
       <c r="R41" t="n">
-        <v>6696663</v>
+        <v>6696943</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5355,17 +5334,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5380,27 +5369,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618199</t>
+          <t>https://artportalen.se/Sighting/128466226</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135618210</v>
+        <v>128466227</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5436,17 +5425,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Länsmansberget, Väster, Dlr</t>
+          <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462664</v>
+        <v>462484</v>
       </c>
       <c r="R42" t="n">
-        <v>6696677</v>
+        <v>6697200</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5470,17 +5459,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5495,24 +5494,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618210</t>
+          <t>https://artportalen.se/Sighting/128466227</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135618226</v>
+        <v>135618199</v>
       </c>
       <c r="B43" t="n">
         <v>57982</v>
@@ -5555,10 +5554,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462624</v>
+        <v>462720</v>
       </c>
       <c r="R43" t="n">
-        <v>6696720</v>
+        <v>6696663</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5621,13 +5620,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618226</t>
+          <t>https://artportalen.se/Sighting/135618199</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135618241</v>
+        <v>135618210</v>
       </c>
       <c r="B44" t="n">
         <v>57982</v>
@@ -5660,7 +5659,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5670,10 +5669,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462640</v>
+        <v>462664</v>
       </c>
       <c r="R44" t="n">
-        <v>6696727</v>
+        <v>6696677</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5710,7 +5709,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5736,13 +5735,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618241</t>
+          <t>https://artportalen.se/Sighting/135618210</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135618331</v>
+        <v>135618226</v>
       </c>
       <c r="B45" t="n">
         <v>57982</v>
@@ -5785,10 +5784,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462724</v>
+        <v>462624</v>
       </c>
       <c r="R45" t="n">
-        <v>6696755</v>
+        <v>6696720</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5851,13 +5850,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618331</t>
+          <t>https://artportalen.se/Sighting/135618226</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135618395</v>
+        <v>135618241</v>
       </c>
       <c r="B46" t="n">
         <v>57982</v>
@@ -5900,10 +5899,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462569</v>
+        <v>462640</v>
       </c>
       <c r="R46" t="n">
-        <v>6696848</v>
+        <v>6696727</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5940,7 +5939,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5966,13 +5965,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618395</t>
+          <t>https://artportalen.se/Sighting/135618241</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135618401</v>
+        <v>135618331</v>
       </c>
       <c r="B47" t="n">
         <v>57982</v>
@@ -6005,7 +6004,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6015,10 +6014,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462589</v>
+        <v>462724</v>
       </c>
       <c r="R47" t="n">
-        <v>6696851</v>
+        <v>6696755</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -6055,7 +6054,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhavk på tall</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6081,13 +6080,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618401</t>
+          <t>https://artportalen.se/Sighting/135618331</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135618420</v>
+        <v>135618395</v>
       </c>
       <c r="B48" t="n">
         <v>57982</v>
@@ -6120,7 +6119,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6130,10 +6129,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462607</v>
+        <v>462569</v>
       </c>
       <c r="R48" t="n">
-        <v>6697017</v>
+        <v>6696848</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -6196,13 +6195,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618420</t>
+          <t>https://artportalen.se/Sighting/135618395</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135618432</v>
+        <v>135618401</v>
       </c>
       <c r="B49" t="n">
         <v>57982</v>
@@ -6235,7 +6234,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6245,10 +6244,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>462608</v>
+        <v>462589</v>
       </c>
       <c r="R49" t="n">
-        <v>6697000</v>
+        <v>6696851</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6285,7 +6284,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhavk på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6311,16 +6310,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135618432</t>
+          <t>https://artportalen.se/Sighting/135618401</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128466230</v>
+        <v>135618420</v>
       </c>
       <c r="B50" t="n">
-        <v>58114</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6328,49 +6327,45 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462362</v>
+        <v>462607</v>
       </c>
       <c r="R50" t="n">
-        <v>6697282</v>
+        <v>6697017</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6394,22 +6389,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6424,27 +6414,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466230</t>
+          <t>https://artportalen.se/Sighting/135618420</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128466231</v>
+        <v>135618432</v>
       </c>
       <c r="B51" t="n">
-        <v>58114</v>
+        <v>57982</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6452,37 +6442,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>462657</v>
+        <v>462608</v>
       </c>
       <c r="R51" t="n">
-        <v>6696882</v>
+        <v>6697000</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6506,22 +6504,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6536,27 +6529,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466231</t>
+          <t>https://artportalen.se/Sighting/135618432</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128466232</v>
+        <v>136208803</v>
       </c>
       <c r="B52" t="n">
-        <v>58114</v>
+        <v>57982</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6564,49 +6557,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462418</v>
+        <v>462440</v>
       </c>
       <c r="R52" t="n">
-        <v>6697314</v>
+        <v>6697233</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6630,22 +6619,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6660,44 +6644,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466232</t>
+          <t>https://artportalen.se/Sighting/136208803</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128466221</v>
+        <v>136209011</v>
       </c>
       <c r="B53" t="n">
-        <v>5199</v>
+        <v>57982</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6706,28 +6690,27 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462534</v>
+        <v>462289</v>
       </c>
       <c r="R53" t="n">
-        <v>6697251</v>
+        <v>6697253</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6751,22 +6734,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6775,34 +6753,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466221</t>
+          <t>https://artportalen.se/Sighting/136209011</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128466247</v>
+        <v>136208807</v>
       </c>
       <c r="B54" t="n">
-        <v>8455</v>
+        <v>57169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6810,37 +6787,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462368</v>
+        <v>462446</v>
       </c>
       <c r="R54" t="n">
-        <v>6697278</v>
+        <v>6697217</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6864,22 +6849,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:50</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:50</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6894,27 +6869,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466247</t>
+          <t>https://artportalen.se/Sighting/136208807</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128466248</v>
+        <v>136208829</v>
       </c>
       <c r="B55" t="n">
-        <v>8455</v>
+        <v>57169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6922,37 +6897,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462651</v>
+        <v>462454</v>
       </c>
       <c r="R55" t="n">
-        <v>6696877</v>
+        <v>6697228</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6976,22 +6963,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7006,65 +6983,73 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466248</t>
+          <t>https://artportalen.se/Sighting/136208829</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128466243</v>
+        <v>136209026</v>
       </c>
       <c r="B56" t="n">
-        <v>79085</v>
+        <v>57169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Länsmansberget Väster, Dlr</t>
+          <t>Länsmansberget, Väster, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462628</v>
+        <v>462266</v>
       </c>
       <c r="R56" t="n">
-        <v>6696967</v>
+        <v>6697230</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7088,22 +7073,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7118,27 +7093,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466243</t>
+          <t>https://artportalen.se/Sighting/136209026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128466244</v>
+        <v>128466230</v>
       </c>
       <c r="B57" t="n">
-        <v>79085</v>
+        <v>58114</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7146,34 +7121,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>462583</v>
+        <v>462362</v>
       </c>
       <c r="R57" t="n">
-        <v>6696944</v>
+        <v>6697282</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7205,7 +7192,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7215,7 +7202,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7241,16 +7228,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128466244</t>
+          <t>https://artportalen.se/Sighting/128466230</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128466245</v>
+        <v>128466231</v>
       </c>
       <c r="B58" t="n">
-        <v>79085</v>
+        <v>58114</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7258,21 +7245,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7282,10 +7269,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462529</v>
+        <v>462657</v>
       </c>
       <c r="R58" t="n">
-        <v>6697126</v>
+        <v>6696882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7317,7 +7304,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7327,7 +7314,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7352,6 +7339,812 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466231</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128466232</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>462418</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6697314</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466232</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128466221</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>462534</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6697251</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466221</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128466247</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>462368</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6697278</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466247</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128466248</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>462651</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6696877</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466248</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128466243</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>462628</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6696967</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466243</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128466244</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>462583</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6696944</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466244</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128466245</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>462529</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6697126</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128466245</t>
         </is>
@@ -7416,6 +8209,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -1630,7 +1630,7 @@
         <v>136208958</v>
       </c>
       <c r="B10" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>135618134</v>
       </c>
       <c r="B17" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>135618145</v>
       </c>
       <c r="B18" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>135618319</v>
       </c>
       <c r="B36" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136208896</v>
       </c>
       <c r="B37" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>135618199</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135618210</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>135618226</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>135618241</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>135618331</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>135618395</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>135618401</v>
       </c>
       <c r="B49" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>135618420</v>
       </c>
       <c r="B50" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>135618432</v>
       </c>
       <c r="B51" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>136208803</v>
       </c>
       <c r="B52" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>136209011</v>
       </c>
       <c r="B53" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>136208807</v>
       </c>
       <c r="B54" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>136208829</v>
       </c>
       <c r="B55" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136209026</v>
       </c>
       <c r="B56" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -1630,7 +1630,7 @@
         <v>136208958</v>
       </c>
       <c r="B10" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136208896</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>136208803</v>
       </c>
       <c r="B52" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>136209011</v>
       </c>
       <c r="B53" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>136208807</v>
       </c>
       <c r="B54" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>136208829</v>
       </c>
       <c r="B55" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136209026</v>
       </c>
       <c r="B56" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 58945-2025 artfynd.xlsx
+++ b/artfynd/A 58945-2025 artfynd.xlsx
@@ -1630,7 +1630,7 @@
         <v>136208958</v>
       </c>
       <c r="B10" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>136208896</v>
       </c>
       <c r="B37" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>136208803</v>
       </c>
       <c r="B52" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>136209011</v>
       </c>
       <c r="B53" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>136208807</v>
       </c>
       <c r="B54" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>136208829</v>
       </c>
       <c r="B55" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136209026</v>
       </c>
       <c r="B56" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
